--- a/data/trans_bre/P1428-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1428-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>3,86</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 8,87</t>
+          <t>1,31; 8,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,71</t>
+          <t>-1,71; 4,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 6,2</t>
+          <t>0,51; 6,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,33</t>
+          <t>1,32; 6,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,64; 255,01</t>
+          <t>16,45; 264,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 216,72</t>
+          <t>-37,23; 197,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 539,96</t>
+          <t>10,78; 636,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,16; 209,55</t>
+          <t>22,74; 222,34</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,7</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>130,8%</t>
+          <t>144,43%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 5,51</t>
+          <t>-1,15; 5,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,88</t>
+          <t>-2,74; 3,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,56</t>
+          <t>-1,85; 3,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,64</t>
+          <t>3,47; 9,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 204,53</t>
+          <t>-24,52; 208,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,48; 145,35</t>
+          <t>-50,88; 135,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 231,44</t>
+          <t>-47,43; 208,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,25; 280,03</t>
+          <t>62,35; 301,12</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,81</t>
+          <t>10,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>301,58%</t>
+          <t>174,99%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,41; 19,63</t>
+          <t>6,8; 19,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 12,91</t>
+          <t>2,42; 13,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 17,6</t>
+          <t>5,33; 18,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 19,03</t>
+          <t>5,79; 16,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76,57; 341,08</t>
+          <t>84,24; 362,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,39; 216,2</t>
+          <t>26,39; 230,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>132,71; 753,59</t>
+          <t>134,06; 713,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>108,77; 1046,38</t>
+          <t>77,1; 344,01</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23,04</t>
+          <t>4,28</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>346,84%</t>
+          <t>64,21%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,6</t>
+          <t>0,33; 6,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,4</t>
+          <t>-2,21; 2,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,63</t>
+          <t>-1,39; 2,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 55,26</t>
+          <t>2,12; 6,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 71,26</t>
+          <t>2,68; 67,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 48,49</t>
+          <t>-33,22; 48,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 65,23</t>
+          <t>-24,36; 66,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,57; 872,85</t>
+          <t>27,19; 106,91</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,85</t>
+          <t>12,64</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>155,93%</t>
+          <t>206,46%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 13,63</t>
+          <t>4,95; 13,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,63</t>
+          <t>5,83; 12,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 10,62</t>
+          <t>4,53; 10,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 14,73</t>
+          <t>10,05; 15,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,62; 208,34</t>
+          <t>45,06; 212,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,21; 312,42</t>
+          <t>77,38; 315,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,3; 299,1</t>
+          <t>71,59; 283,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>76,71; 278,21</t>
+          <t>126,09; 331,14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19,25</t>
+          <t>18,83</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4529,72%</t>
+          <t>4319,87%</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,45; 26,6</t>
+          <t>21,26; 26,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,86; 20,9</t>
+          <t>14,55; 20,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,86; 15,44</t>
+          <t>10,94; 15,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,03; 21,69</t>
+          <t>16,45; 21,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>930,64; 9528,77</t>
+          <t>930,35; 9669,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>333,06; 5449,92</t>
+          <t>310,31; 5223,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1233,76; —</t>
+          <t>1169,58; —</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14,25</t>
+          <t>9,17</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>283,98%</t>
+          <t>175,0%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,99; 12,0</t>
+          <t>8,72; 12,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,69</t>
+          <t>5,93; 8,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,57; 7,14</t>
+          <t>4,57; 6,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,95; 29,86</t>
+          <t>8,08; 10,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>112,09; 180,91</t>
+          <t>111,76; 179,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>101,76; 191,28</t>
+          <t>101,5; 188,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>108,7; 222,68</t>
+          <t>109,81; 221,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>167,16; 669,89</t>
+          <t>139,24; 221,04</t>
         </is>
       </c>
     </row>
